--- a/static/modelo_planilha.xlsx
+++ b/static/modelo_planilha.xlsx
@@ -1,38 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9d0867bf1a72efb/Documentos/Lab_LEP/static/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_0A1379904F778EE69A0FA3D873C6119571085A4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BFF3104-C83E-45C2-A456-2647ADAF9589}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="22932" yWindow="-192" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materiais" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamentos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experimentos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternativas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Parametros" sheetId="1" r:id="rId1"/>
+    <sheet name="Materiais" sheetId="2" r:id="rId2"/>
+    <sheet name="Equipamentos" sheetId="3" r:id="rId3"/>
+    <sheet name="Experimentos" sheetId="4" r:id="rId4"/>
+    <sheet name="Alternativas" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>tempo</t>
+  </si>
+  <si>
+    <t>rendimento</t>
+  </si>
+  <si>
+    <t>energia</t>
+  </si>
+  <si>
+    <t>mao_obra</t>
+  </si>
+  <si>
+    <t>outros</t>
+  </si>
+  <si>
+    <t>quantidade_produzida</t>
+  </si>
+  <si>
+    <t>Projeto proposto</t>
+  </si>
+  <si>
+    <t>quantidade</t>
+  </si>
+  <si>
+    <t>preco</t>
+  </si>
+  <si>
+    <t>Reagente A</t>
+  </si>
+  <si>
+    <t>Reagente B</t>
+  </si>
+  <si>
+    <t>horas</t>
+  </si>
+  <si>
+    <t>custo_hora</t>
+  </si>
+  <si>
+    <t>Espectrofotômetro</t>
+  </si>
+  <si>
+    <t>Estufa</t>
+  </si>
+  <si>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>custo</t>
+  </si>
+  <si>
+    <t>Método tradicional</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,80 +117,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,73 +419,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rendimento</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mao_obra</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>outros</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>quantidade_produzida</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Projeto proposto</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>150</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>800</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>100</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>50</v>
       </c>
     </row>
@@ -488,54 +484,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>quantidade</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>preco</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Reagente A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="n">
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
         <v>25.5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reagente B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>40</v>
       </c>
     </row>
@@ -545,54 +531,45 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>horas</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>custo_hora</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Espectrofotômetro</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
         <v>8</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>30</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Estufa</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
         <v>12</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>10</v>
       </c>
     </row>
@@ -602,38 +579,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>12.4</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>12.7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>12.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>12.6</v>
       </c>
     </row>
@@ -643,49 +617,41 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>custo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rendimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Método tradicional</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
         <v>2200</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>10</v>
       </c>
     </row>

--- a/static/modelo_planilha.xlsx
+++ b/static/modelo_planilha.xlsx
@@ -1,104 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9d0867bf1a72efb/Documentos/Lab_LEP/static/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_0A1379904F778EE69A0FA3D873C6119571085A4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BFF3104-C83E-45C2-A456-2647ADAF9589}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-192" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parametros" sheetId="1" r:id="rId1"/>
-    <sheet name="Materiais" sheetId="2" r:id="rId2"/>
-    <sheet name="Equipamentos" sheetId="3" r:id="rId3"/>
-    <sheet name="Experimentos" sheetId="4" r:id="rId4"/>
-    <sheet name="Alternativas" sheetId="5" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materiais" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamentos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experimentos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternativas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investimento" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FluxoCaixa" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
-  <si>
-    <t>nome</t>
-  </si>
-  <si>
-    <t>tempo</t>
-  </si>
-  <si>
-    <t>rendimento</t>
-  </si>
-  <si>
-    <t>energia</t>
-  </si>
-  <si>
-    <t>mao_obra</t>
-  </si>
-  <si>
-    <t>outros</t>
-  </si>
-  <si>
-    <t>quantidade_produzida</t>
-  </si>
-  <si>
-    <t>Projeto proposto</t>
-  </si>
-  <si>
-    <t>quantidade</t>
-  </si>
-  <si>
-    <t>preco</t>
-  </si>
-  <si>
-    <t>Reagente A</t>
-  </si>
-  <si>
-    <t>Reagente B</t>
-  </si>
-  <si>
-    <t>horas</t>
-  </si>
-  <si>
-    <t>custo_hora</t>
-  </si>
-  <si>
-    <t>Espectrofotômetro</t>
-  </si>
-  <si>
-    <t>Estufa</t>
-  </si>
-  <si>
-    <t>valor</t>
-  </si>
-  <si>
-    <t>custo</t>
-  </si>
-  <si>
-    <t>Método tradicional</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -117,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,62 +414,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rendimento</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>energia</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mao_obra</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>quantidade_produzida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Projeto proposto</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>150</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>800</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -484,44 +490,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>quantidade</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>preco</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reagente A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>10</v>
       </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>25.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reagente B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>40</v>
       </c>
     </row>
@@ -531,45 +547,54 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>custo_hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Espectrofotômetro</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Estufa</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -579,35 +604,38 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>12.4</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>12.7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>12.5</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>12.6</v>
       </c>
     </row>
@@ -617,42 +645,148 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>custo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tempo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rendimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Método tradicional</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>investimento_inicial</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>taxa_desconto</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valor_residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>2200</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
+      <c r="B3" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/static/modelo_planilha.xlsx
+++ b/static/modelo_planilha.xlsx
@@ -7,13 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materiais" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamentos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experimentos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alternativas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investimento" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FluxoCaixa" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Globais" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamentos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculado_pelo_site" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,13 +29,39 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0013293D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3EAEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,8 +76,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,69 +455,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rendimento</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mao_obra</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>outros</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>quantidade_produzida</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Planilha-modelo — somente valores digitados</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Projeto proposto</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>150</v>
-      </c>
-      <c r="E2" t="n">
-        <v>800</v>
-      </c>
-      <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="n">
-        <v>50</v>
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>• Células amarelas são as que você preenche. Nada nesta planilha é calculado: o site calcula sozinho tudo o que o Excel original calculava (veja a aba Calculado_pelo_site).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>• Aba Globais: parâmetros que valem para todos os cenários.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>• Aba Cenarios: uma coluna por cenário. Para adicionar um cenário, crie uma nova coluna à direita (o nome do cenário é o título da coluna).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>• Aba Equipamentos: uma linha por equipamento; a coluna 'cenario' deve repetir exatamente o nome do cenário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>• Não altere os nomes das abas nem a coluna 'chave' (o site usa essas chaves para ler os valores).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>• Os valores vêm de Teste.xlsx e servem de exemplo: substitua pelos seus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>• FCI e edificações (aba Cenarios) são opcionais e NÃO existiam em Teste.xlsx. Sem FCI, o site usa o custo de equipamentos como investimento e avisa que o resultado é preliminar.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -495,50 +531,735 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>quantidade</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>preco</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>chave</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>variavel</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>unidade</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Reagente A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste de custo de equipamentos (índice CEPCI)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reagente B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
+          <t>cepci_ano_base</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ano-base do custo de referência</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cepci_base</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Índice CEPCI do ano-base</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>576.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cepci_ano_atual</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ano atual</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cepci_atual</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Índice CEPCI do ano atual</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>índice</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>799.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Custos unitários</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>custo_lupulo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Matéria-prima (lúpulo)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US$/t</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>etanol_preco</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Etanol — preço de lista</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US$/t</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>etanol_desconto</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Etanol — desconto</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>co2_preco</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CO₂ — preço de lista</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US$/t</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>co2_desconto</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CO₂ — desconto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>energia_eletrica</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Energia elétrica</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US$/kWh</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>residuos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Descarte de resíduos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US$/t</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mao_obra_hora</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mão de obra operacional (com encargos)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US$/h</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>agua</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US$/kg</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Critérios financeiros</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vida_equipamentos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vida útil dos equipamentos (depreciação linear)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>vida_edificacoes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vida útil das edificações (depreciação linear)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>imposto</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Imposto local sobre o lucro antes do imposto</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>marr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Taxa mínima de atratividade (MARR)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>wacc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Custo médio ponderado de capital (WACC)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>valor_residual_pct</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Valor residual (% do custo das edificações)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vida_projeto</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vida útil do projeto</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>anos</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Critérios de custo (percentuais)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>manutencao</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Manutenção e reparos</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>% do capital fixo (FCI)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>suprimentos</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Suprimentos operacionais</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>% da manutenção</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>laboratorio</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Encargos de laboratório</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>% da mão de obra operacional</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>patentes</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Patentes e royalties</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>% da receita</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>contingencia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Contingência</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>% do capital fixo (FCI)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>impostos_locais</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Impostos locais</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>% do capital fixo (FCI)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>seguro</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>% do capital fixo (FCI)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>embalagem</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Embalagem</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>% da mão de obra operacional + manutenção</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mao_obra_indireta</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mão de obra indireta</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>% da mão de obra operacional + manutenção</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>40</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>armazenagem</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Armazém e estocagem</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>% da mão de obra operacional + manutenção</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>administrativas</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Despesas administrativas</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>% do custo de manufatura</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>vendas</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Despesas de vendas e distribuição</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>% da receita</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pd</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pesquisa e desenvolvimento</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>% da receita</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -552,51 +1273,400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>horas</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>custo_hora</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>chave</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>variavel</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>unidade</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>CO2 Supercrítico</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Espectrofotômetro</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Estufa</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
+          <t>capacidade</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Matéria-prima processada (entrada)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>horas_dia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Duração do turno</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>horas/dia</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dias_ano</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dias de operação por ano</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dias/ano</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>operadores</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operadores por turno</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>nº</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Produtos e receitas</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>produto1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Produto 1 (saída) — extrato</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.8884316390400001</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.62442458496</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>preco_produto1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Preço do produto 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US$/kg</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>512.22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>produto2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Produto 2 (saída) — farelo desengordurado</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3.64251941504</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>preco_produto2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Preço do produto 2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US$/kg</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Insumos e utilidades</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>etanol</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reagente: etanol</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>co2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Reagente: CO₂</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>112.5820373568</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>agua</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Água</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>135.57</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>100.0065</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>residuos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Descarte de resíduos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>t/ano</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.1600104</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.1600104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Investimento (opcional — não consta na planilha)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fci</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Investimento de capital fixo — FCI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>edificacoes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Custo das edificações</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -609,34 +1679,501 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>valor</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>cenario</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>equipamento</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>quantidade</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>custo_unidade_usd</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>capacidade</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>unidade_capacidade</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>consumo_kwh_ano</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>ajustar_cepci</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>12.4</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Lavador (sem cotação)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>kg/h</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>macanuda.com.br (lavador de alface)</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>12.7</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Centrífuga (sem cotação)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>12.5</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Secador / desidratador (sem cotação)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>macanuda.com.br (desidratador)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>12.6</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Extrator etanol</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>22500</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>kg/h</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>990</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>laboao</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Evaporador</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>33800</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>L/h</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>400.4710348881696</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>aço inox tubos</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>timerhaus</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Extração via solvente EtOH puro</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Secador (ábaco, sem valor)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>ft2</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>aço carbono</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>timerhaus / matche.com</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CO2 Supercrítico</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Lavador (sem cotação)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>kg/h</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>macanuda.com.br (lavador de alface)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CO2 Supercrítico</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Centrífuga</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>10999</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CO2 Supercrítico</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Secador</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5052.55</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>6097.926527168509</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>macanuda.com.br (desidratador)</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CO2 Supercrítico</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Extrator supercrítico</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>55805</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>L/h</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>740.8309258350001</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>aço inox</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Labsolutions</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -650,143 +2187,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>custo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tempo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>rendimento</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Item calculado</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Onde estava em Teste.xlsx</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Como o site calcula</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Método tradicional</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2200</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>investimento_inicial</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>taxa_desconto</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>valor_residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n">
-        <v>300</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>800</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Razão CEPCI</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!K6</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>índice CEPCI atual ÷ índice CEPCI do ano-base</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>900</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Valor ajustado do equipamento</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!E13:E23 (=D ou =D×K6)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>custo unitário; multiplicado pela razão CEPCI quando 'ajustar_cepci' = sim</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1000</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Custo total do equipamento</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!F13:F23</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>valor ajustado × quantidade</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1000</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Custo total de equipamentos do cenário</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!D19/F19 e D24/F24</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>soma dos custos totais dos equipamentos do cenário</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Consumo elétrico do cenário</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!I19, I24 e Tecno Assumptions!D23:E23</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>soma do consumo elétrico (kWh/ano) dos equipamentos do cenário</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Rendimento do processo 1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Tecno Assumptions!D17:E17</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>produto 1 ÷ matéria-prima processada</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Rendimento do processo 2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tecno Assumptions!D18:E18</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>produto 2 ÷ matéria-prima processada</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Preço final do etanol e do CO₂</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Tecno Assumptions!D33:D34 (=500-500*10%, =100-10%*100)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>preço de lista × (1 − desconto). Preço e desconto agora são dois campos digitados</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Preço dos produtos em US$/t</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Tecno Assumptions!D40:E41 (=250*1000 etc.)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>preço em US$/kg × 1.000. Você digita o preço em US$/kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NÃO replicado: total geral de equipamentos e consumo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Custo dos Equipamentos!F39 e I39</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>No Excel, F39 = SUM(F13:F38) soma os itens E os subtotais (F19, F24), contando tudo em dobro (256.313 em vez de 128.157); além disso, soma cenários que são alternativas entre si. O site mostra o total por cenário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Acrescentado pelo site (não estava no Excel)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>receita, custos anuais pelos critérios percentuais, depreciação linear, imposto, fluxo de caixa, VP, VF, VPL, TIR, payback e veredito de viabilidade</t>
+        </is>
       </c>
     </row>
   </sheetData>
